--- a/04_DESIGN_TABLES/DesignTable_2405.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2405.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3272,24 +3277,73 @@
           <t>2405-10-06</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="J35" t="n">
+        <v>60</v>
+      </c>
+      <c r="K35" t="n">
+        <v>37</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.484</v>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>2405-10-06</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>7/8-14</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-10-06 col "L LGTH" = "1.670" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 506.2, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 28/32 rows with an Air-Way/OMi value agree with this catalog column to rounding (4 differ, e.g. 2405-03-04 1.32 vs 1.31); HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-10-06 col "C HEX" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 506.2, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 32/32 rows with an Air-Way/OMi value agree with this catalog column to rounding; D3@BORE_THRU: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-10-06 col "B1 DRILL" = "0.484" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 506.2, page verified) [Brennan = yes 2026-10-18] - through bore from the JIC end; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 32/32 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_B@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; JIC_RELIEFL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JIC_THDZ@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JIC_CONEDIA@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JIC_LANDL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JIC_SEATL@DRIVE: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; FPT_P1@DRIVE: end library gen_straight2 FPT[6] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.57, FPT_P1 0.68 = MS51503 P1 max) - port depth = MS51503 P1 max per pipe dash (end detail) [Q-TRANSFER-ENDLIB yes]; TAPDRILL@BORE_A: end library gen_straight2 FPT[6] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.57, FPT_P1 0.68 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; $PRP@EndA_Thread: end library gen_straight2 FPT[6] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.57, FPT_P1 0.68 = MS51503 P1 max) thread text; $PRP@EndB_Thread: end library gen_straight2 JIC[10] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L2 / hex / D3 from the Brennan TFA catalog p7 alone; JIC end + port depth from the end library; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -3300,6 +3354,11 @@
       <c r="V35" t="inlineStr">
         <is>
           <t>2405-10-06</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -3309,24 +3368,73 @@
           <t>2405-14-12</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.1875</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J36" t="n">
+        <v>60</v>
+      </c>
+      <c r="K36" t="n">
+        <v>37</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.719</v>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>2405-14-12</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1 3/16-12</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L2@DRIVE: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-14-12 col "L LGTH" = "2.06" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 586.9, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 28/32 rows with an Air-Way/OMi value agree with this catalog column to rounding (4 differ, e.g. 2405-03-04 1.32 vs 1.31); HEXB@HEX: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-14-12 col "C HEX" = "1.375" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 586.9, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 32/32 rows with an Air-Way/OMi value agree with this catalog column to rounding; D3@BORE_THRU: Brennan TFA catalog p7 table TFA-p007-t02 "2405 MJ-FP STRAIGHT" row 2405-14-12 col "B1 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 586.9, page verified) [Brennan = yes 2026-10-18] - through bore from the JIC end; mapping: TFA p7 2405 drawing: L = overall, C HEX = body hex, B1 DRILL = through bore from the JIC end (impact/F2a.json, certain); same-table check on today's base: 32/32 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_B@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; JIC_RELIEFL@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] RL (end detail per dash); JIC_THDZ@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] TZ (end detail per dash); JIC_CONEDIA@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] CD (end detail per dash); JIC_LANDL@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] LL (end detail per dash); JIC_SEATL@DRIVE: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] SL (end detail per dash); RELIEFANG@DRIVE: gen_straight2 end_JICM constant 60 deg relief ramp (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; SEATB@DRIVE: gen_straight2 end_JICM constant 37 deg flare seat (the value on every built row of this table) [Q-TRANSFER-ENDLIB yes]; FPT_P1@DRIVE: end library gen_straight2 FPT[12] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.91, FPT_P1 0.91 = MS51503 P1 max) - port depth = MS51503 P1 max per pipe dash (end detail) [Q-TRANSFER-ENDLIB yes]; TAPDRILL@BORE_A: end library gen_straight2 FPT[12] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.91, FPT_P1 0.91 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; $PRP@EndA_Thread: end library gen_straight2 FPT[12] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.91, FPT_P1 0.91 = MS51503 P1 max) thread text; $PRP@EndB_Thread: end library gen_straight2 JIC[14] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread text</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L2 / hex / D3 from the Brennan TFA catalog p7 alone; JIC end + port depth from the end library; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -3337,6 +3445,11 @@
       <c r="V36" t="inlineStr">
         <is>
           <t>2405-14-12</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
